--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V247"/>
+  <dimension ref="A1:AB269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,36 @@
           <t>de.wikipedia.org</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>www.stolpersteine-berlin.de</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>apps.bundesarchiv.de</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>collections.yadvashem.org</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>commons.wikimedia.org</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>atom.lib.uct.ac.za</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>www.lotta-magazin.de</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2867,6 +2897,11 @@
           <t>11 giessen marktplatz</t>
         </is>
       </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Marktplatz 11</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>50.58727</t>
@@ -4514,6 +4549,16 @@
           <t>GO</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2944820/breidenbach.html</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4721,6 +4766,16 @@
           <t>GO</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2825297/stuttgart.html</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1022</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5240,6 +5295,16 @@
           <t>GO</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/12217751/theresienstadt-concentration-camp-and-ghetto.html</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q160175</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6785,6 +6850,523 @@
         </is>
       </c>
     </row>
+    <row r="248"/>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Steinstraße 19,</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>19 steinstraße</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Wullenweberstraße 11, Berlin-Moabit</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>11 berlinmoabit wullenweberstraße</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2950159</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>https://www.stolpersteine-berlin.de/de/wullenweberstr/11/auguste-stern</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Wölfersheim</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>wölfersheim</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2806852/woelfersheim.html</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q634098</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Koblenz</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>koblenz</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>https://apps.bundesarchiv.de/gedenkbuch/de976422</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Yad Vashem</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>vashem yad</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>https://collections.yadvashem.org/en/names/13219727</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Baiertal</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>baiertal</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2953189/baiertal.html</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7904</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Lollar</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>lollar</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6557780</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>states united</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6252001/united-states.html</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Berdytschiw</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>berdytschiw</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/712441/berdychiv.html</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7904</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Oberhessen</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>oberhessen</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15837262</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Marktplatz 11</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>11 marktplatz</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Walltorstraße 48</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>48 walltorstraße</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>KZ Buchenwald</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>buchenwald kz</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Buchenwald</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/8644023/konzentrationslager-buchenwald.html</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q152802</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>darmstadt</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2938913/darmstadt.html</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2973</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Treblinka (Vernichtungslager)</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>treblinka vernichtungslager</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/756807/treblinka.html</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q152010</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Gießen Marktplatz 15</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>15 gießen marktplatz</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2920512</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/Erleben/Über-Gießen/Stolpersteine/Marktplatz-15</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Stolperstein_Gießen_Marktplatz_15_Esther_Stern.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Sennfeld (Adelsheim)</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>adelsheim sennfeld</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Sennfeld</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2833011/sennfeld.html</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q14531586</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>aus Gießen nach Palästina</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>aus gießen nach palästina</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>https://atom.lib.uct.ac.za/uploads/r/university-of-cape-town-libraries-special-collections/a/3/c/a3cc8572f727d61327e4f929a86fc91c339c13cc41721aa18c8f158e13678891/mss_sahgf_schragenheim_publications_025_1-20.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Gießen Schillerschule (Volksschule)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>gießen schillerschule volksschule</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2967.1&amp;object=tx%2C2874.2967.1</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Datei:Stolperstein_Gießen_Nordanlage_Esther_Stern.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Esther-Stern-Platz Gießen</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>esthersternplatz gießen</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Gießen</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>https://www.lotta-magazin.de/ausgabe/1/den-ermordeten-menschen-ein-gesicht-geben/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="locations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP82"/>
+  <dimension ref="A1:BN69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,1996 +434,3084 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>wider_region</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>coordinate_source</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>lat</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>label</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>www.geonames.org</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>www.wikidata.org</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>www.giessen.de</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>gedenkbuch.saarbruecken.de</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tinyurl.com</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>www.facebook.com</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>en.wikipedia.org</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>archiv.schillerschule.de</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>it.wikipedia.org</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>www.alte-zigarrenfabrik.com</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>www.museum.de</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>www.myheritage.it</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>www.sommer-archive.com</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>obits.syracuse.com</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>ballweg.store.helloflowers.com</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>de.wikipedia.org</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>www.stolpersteine-berlin.de</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>apps.bundesarchiv.de</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>collections.yadvashem.org</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>commons.wikimedia.org</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>atom.lib.uct.ac.za</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>www.lotta-magazin.de</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>cja.huji.ac.il</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>www.nli.org.il</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>jewishvirtuallibrary.org</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>www.duden.de</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>www.buchenwald.de</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>www.rheinische-geschichte.lvr.de</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>alte-synagoge-wuppertal.de</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>hachschara.juedische-geschichte-online.net</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>www.jewish-places.de</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>www.ben-shemen.org.il</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>encyclopedia.ushmm.org</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>www.sachsenhausen-sbg.de</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>www.manchesterjewishstudies.org</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>encyclopedia.yivo.org</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>carl-fuhlrott-gymnasium.de</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>www.wuppertal.de</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>herder-schule.de</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>www.juedisches-europa.net</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>www.gedenktafeln-in-berlin.de</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>adassjisroel.de</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>en.huji.ac.il</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>www.zionistarchives.org.il</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>www.archives.gov.il</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>www.lbi.org</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>www.yadvashem.org</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>prabook.com</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>irgun-jeckes.org</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>cris.tau.ac.il</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>en.jabotinsky.org</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>www.liebknecht-gymnasium.de</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>www.dhm.de</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>www.gdw-berlin.de</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>kiju-aliyah.de</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>youthaliyah.org.uk</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>www.frankfurt-oder-juedisch.de</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>www.orte-der-erinnerung.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bahnhof, Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>am bahnhof frankfurt main</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>50.11035</v>
+      </c>
+      <c r="G2" t="n">
+        <v>8.671849999999999</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6553153</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1794</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gießen</t>
+          <t>Baiertal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gießen</t>
+          <t>baiertal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.866666666667</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.65</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2938913/darmstadt.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>49.2944</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.7889</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2973</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2953189/baiertal.html</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7904</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Schlesien</t>
+          <t>Barmen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>schlesien</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+          <t>barmen</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>51.2773</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.198</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2952539/barmen.html</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q153974</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Belgien</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>berlin</t>
+          <t>belgien</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.516666666667</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>13.383333333333</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2950159/berlin.html</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>50.6402809</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.6667145</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q64</t>
+          <t>reise_zurueck</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Frankfurt/M</t>
+          <t>Ben Shemen  - Kinderdorf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>frankfurtm</t>
+          <t>ben kinderdorf shemen</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ben Shemen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>50.11055555555556</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Ben Shemen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8.682222222222222</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>31.959</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34.9278</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1794</t>
+          <t>neue_heimat
+Ort der Zeit</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/maps/google_31.959_34.9278.html</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2777009</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Kinder-_und_Jugenddorf_Ben_Shemen</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>https://www.ben-shemen.org.il/en</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Berdytschiw</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>am frankfurt main</t>
+          <t>berdytschiw</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50.11055555555556</t>
+          <t>GO – geographischer Ort &gt; Russland / Ukraine &gt; Ukraine</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.682222222222222</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>49.8989</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28.6011</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1794</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/712441/berdychiv.html</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q7904</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kehl am Rhein</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>am kehl rhein</t>
+          <t>berlin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.571111111111</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.8088888888889</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2891951/kehl.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>52.5034</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.3815</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q15979</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2950159/berlin.html</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q64</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Stern%E2%80%99sches_Konservatorium</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>https://www.gedenktafeln-in-berlin.de/gedenktafeln/detail/juedische-private-musikschule-hollaender/1040</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>https://adassjisroel.de/gestern/schulwerk-der-adass-jisroel/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brücke Kehl–Straßburg (Rheinquerung)</t>
+          <t>Bombay</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>brücke kehlstraßburg rheinquerung</t>
+          <t>bombay</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.5737</t>
+          <t>GO – geographischer Ort &gt; India &gt; Maharashtra &gt; Mumbai</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.80194</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>19.07283</v>
+      </c>
+      <c r="G9" t="n">
+        <v>72.88261</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>verkehrsmittel</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1375288</t>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/1275339/mumbai.html</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1156</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Breidenbach</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>breidenbach</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.29695 </t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.38107 </t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>50.8722</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.4053</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2944820/breidenbach.html</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kibbuz Rodges, besteht nicht mehr (in der Nähe von Petah Tikva)</t>
+          <t>Breslau</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>besteht der in kibbuz mehr nicht nähe petah rodges tikva von</t>
+          <t>breslau</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>Schlesien</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Schlesien</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 34.9</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>51.1028</v>
+      </c>
+      <c r="G11" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3081368</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1799</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>https://cja.huji.ac.il/hmm/browser.php?mode=set&amp;id=58391</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>https://www.buchenwald.de/</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>https://www.gedenktafeln-in-berlin.de/gedenktafeln/detail/haus-der-zionistischen-organisationen/1012</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ēmeq Yizrəʿēl</t>
+          <t>Brücke Kehl–Straßburg (Rheinquerung)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yizrəʿēl ēmeq</t>
+          <t>brücke kehlstraßburg rheinquerung</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kehl</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>32.596388888889</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Kehl</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.241944444444</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/293165/jezreel-valley.html</t>
-        </is>
+          <t>wikidata</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>48.5737</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.80194</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q763829</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1375288</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kibbuz Ein HaNetziv</t>
+          <t>Buchenwald</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ein hanetziv kibbuz</t>
+          <t>buchenwald</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32.470197222222</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.5024</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/295211/-en-hanaziv.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>50.903</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.0758</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2095906</t>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/13665267/aussenlager-abteroda-konzentrationslager-buchenwald.html</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q152802</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>https://www.buchenwald.de/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Darmstadt</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>haifa</t>
+          <t>darmstadt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32.583333333333</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/294800/haifa.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>49.8728</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.651199999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q185845</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2938913/darmstadt.html</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2973</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kibbuz Tirat Tsvi</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>kibbuz tirat tsvi</t>
+          <t>deutschland</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32.421944444444</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.528333333333</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/293304/tirat-tsvi.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q550025</t>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2921044/federal-republic-of-germany.html</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q183</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Elberfeld</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>italien</t>
+          <t>elberfeld</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>51.2508</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.1481</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3081368/wroclaw.html</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1799</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Kameraden,_deutsch-j%C3%BCdischer_Wanderbund</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>https://hachschara.juedische-geschichte-online.net/en/organization/gnd/10090732-5</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>https://carl-fuhlrott-gymnasium.de/</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>https://www.wuppertal.de/denkmalliste-online/Detail/Show/2218</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>https://herder-schule.de/schulgeschichte/</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>https://www.juedisches-europa.net/archiv-seite-4-1/3-2019/j%C3%BCdische-jugendbewegung/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Esther-Stern-Platz Gießen</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>deutschland</t>
+          <t>esthersternplatz gießen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2921044/federal-republic-of-germany.html</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>50.5862066</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.6742306</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q183</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://www.lotta-magazin.de/ausgabe/1/den-ermordeten-menschen-ein-gesicht-geben/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>Frankfurt (Main) Hauptbahnhof</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>belgien</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
+          <t>frankfurt hauptbahnhof main</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>50.1042</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.657500000000001</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6290300/frankfurt-hauptbahnhof.html</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q165368</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Niederlande</t>
+          <t>Frankfurt an der Oder</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>niederlande</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
+          <t>an der frankfurt oder</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Brandenburg</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>52.3471</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14.5506</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2925534</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q154498</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Kameraden,_deutsch-j%C3%BCdischer_Wanderbund</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>https://www.juedisches-europa.net/archiv-seite-4-1/3-2019/j%C3%BCdische-jugendbewegung/</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>http://www.zionistarchives.org.il/en/familyresearch/GenealogyDatabases/Pages/YouthImmigration.aspx</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>https://www.liebknecht-gymnasium.de/schulprofil/zur-geschichte-der-schule.html</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>https://www.dhm.de/lemo/kapitel/ns-regime/ns-organisationen/bund-deutscher-maedel</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>https://www.gdw-berlin.de/vertiefung/themen/13-widerstand-von-jugendlichen</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>https://kiju-aliyah.de/historie/</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>https://youthaliyah.org.uk/about#history</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>https://www.frankfurt-oder-juedisch.de/homepage/menschen/dr-hermann-neumark/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Klein-Linden</t>
+          <t>Frankfurt/M</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kleinlinden</t>
+          <t>frankfurtm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.560277777778</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.6461111111111</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2888549/klein-linden.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>50.11</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.68</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1571834</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Großen-Linden</t>
+          <t>Frankreich</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>großenlinden</t>
+          <t>frankreich</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>50.528113</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8.6620145</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>46</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>reise_zurueck</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/11974166/grossen-linden.html</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q116016915</t>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3017382/republic-of-france.html</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q142</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Breidenbach</t>
+          <t>Genua</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>breidenbach</t>
+          <t>genua</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Genova</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50.8833</t>
+          <t>GO – geographischer Ort &gt; Italia &gt; Liguria &gt; Genova</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8.466669444444445</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2944820/breidenbach.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>44.4047</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.9443</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q564579</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3176219/genoa.html</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1449</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Steinstraße 19,</t>
+          <t>Gießen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19 steinstraße</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
+          <t>gießen</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>50.5849</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.6724</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2938913/darmstadt.html</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2973</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wullenweberstraße 11, Berlin-Moabit</t>
+          <t>Gießen Marktplatz 15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11 berlinmoabit wullenweberstraße</t>
+          <t>15 gießen marktplatz</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.52437</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.41053</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>50.58727</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.67554</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>erinnerungsort</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2950159</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>https://www.stolpersteine-berlin.de/de/wullenweberstr/11/auguste-stern</t>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2920512</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/Erleben/Über-Gießen/Stolpersteine/Marktplatz-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Stolperstein_Gießen_Marktplatz_15_Esther_Stern.JPG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wölfersheim</t>
+          <t>Gießen Schillerschule (Volksschule)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wölfersheim</t>
+          <t>gießen schillerschule volksschule</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.3975</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.8113888888889</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>50.5898867</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.6748519</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>alte_heimat</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2806852/woelfersheim.html</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q634098</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2967.1&amp;object=tx%2C2874.2967.1</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Datei:Stolperstein_Gießen_Nordanlage_Esther_Stern.JPG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Theresienstadt</t>
+          <t>Großen-Linden</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>theresienstadt</t>
+          <t>großenlinden</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.510278</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.149722</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/12217751/theresienstadt-concentration-camp-and-ghetto.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>50.52785</v>
+      </c>
+      <c r="G26" t="n">
+        <v>8.662000000000001</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q160175</t>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/11974166/grossen-linden.html</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q116016915</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Koblenz</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>koblenz</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>https://apps.bundesarchiv.de/gedenkbuch/de976422</t>
+          <t>haifa</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>32.5833</v>
+      </c>
+      <c r="G27" t="n">
+        <v>35</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/294800/haifa.html</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q185845</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Yad Vashem</t>
+          <t>Haifa, Universität, Bibliothek</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>vashem yad</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://collections.yadvashem.org/en/names/13219727</t>
+          <t>bibliothek haifa universität</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Haifa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Haifa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>32.8191218</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.9983856</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Baiertal</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>baiertal</t>
+          <t>italien</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Campello sul Clitunno</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.574930555556</t>
+          <t>GO – geographischer Ort &gt; Italia &gt; Umbria &gt; Campello sul Clitunno</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8.7090277777778</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2953189/baiertal.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>42.8333</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12.8333</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q7904</t>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3175395</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q38</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lollar</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lollar</t>
+          <t>jerusalem</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8.7</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6557780</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>31.769</v>
+      </c>
+      <c r="G30" t="n">
+        <v>35.2163</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/281184</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1218</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/en/archives/NNL_CAHJP997013170218605171/NLI</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>https://jewishvirtuallibrary.org/jsource/judaica/ejud_0002_0020_0_20210.html</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>https://www.duden.de/rechtschreibung/Restitution</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>https://en.huji.ac.il/</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>http://www.zionistarchives.org.il/en/pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov.il/</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>https://www.lbi.org/about/lbi-international/</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/de/about/yad-vashem.html</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>https://prabook.com/web/paul.alsberg/570050</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Kehl am Rhein</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>states united</t>
+          <t>am kehl rhein</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Kehl</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>39.828175</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Kehl</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-98.5795</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6252001/united-states.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>48.57297</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7.81523</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2891951/kehl.html</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15979</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Berdytschiw</t>
+          <t>Kibbuz</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>berdytschiw</t>
+          <t>kibbuz</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>50.574930555556</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.7090277777778</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/712441/berdychiv.html</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q7904</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>31.9522788</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.921944</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Oberhessen</t>
+          <t>Kibbuz Ein HaNetziv</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>oberhessen</t>
-        </is>
+          <t>ein hanetziv kibbuz</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ein HaNetziv</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz &gt; Ein HaNetziv</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>32.4715</v>
+      </c>
+      <c r="G33" t="n">
+        <v>35.50014</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q15837262</t>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/295211/-en-hanaziv.html</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2095906</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marktplatz 11</t>
+          <t>Kibbuz Rodges, besteht nicht mehr (in der Nähe von Petah Tikva)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>11 marktplatz</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+          <t>besteht der in kibbuz mehr nicht nähe petah rodges tikva von</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kibbuz Rodges</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz &gt; Kibbuz Rodges</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>32.0877639</v>
+      </c>
+      <c r="G34" t="n">
+        <v>34.8859985</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Löberstraße 20</t>
+          <t>Kibbuz Tirat Tsvi</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20 löberstraße</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
+          <t>kibbuz tirat tsvi</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tirat Tsvi</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz &gt; Tirat Tsvi</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>32.42131</v>
+      </c>
+      <c r="G35" t="n">
+        <v>35.52791</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+          <t>https://www.geonames.org/293304/tirat-tsvi.html</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q550025</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Walltorstraße 48</t>
+          <t>Klein-Linden</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>48 walltorstraße</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
+          <t>kleinlinden</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Giessen</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>50.55685</v>
+      </c>
+      <c r="G36" t="n">
+        <v>8.647119999999999</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2888549/klein-linden.html</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1571834</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>stuttgart</t>
+          <t>koblenz</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>48.7775</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Koblenz</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2825297/stuttgart.html</t>
-        </is>
+          <t>wikidata</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>53.2525</v>
+      </c>
+      <c r="G37" t="n">
+        <v>10.414444444444</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1022</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q3920</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>https://apps.bundesarchiv.de/gedenkbuch/de976422</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Frankfurt (Main) Hauptbahnhof</t>
+          <t>KZ Buchenwald</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>frankfurt hauptbahnhof main</t>
+          <t>buchenwald kz</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Buchenwald</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>50.10679</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Buchenwald</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8.66317</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6290300/frankfurt-hauptbahnhof.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>51.0214</v>
+      </c>
+      <c r="G38" t="n">
+        <v>11.2486</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q165368</t>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/8644023/konzentrationslager-buchenwald.html</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q152802</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KZ Buchenwald</t>
+          <t>Lollar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>buchenwald kz</t>
+          <t>lollar</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Buchenwald</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>51.02262</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>11.24923</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/8644023/konzentrationslager-buchenwald.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q152802</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6557780</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q625061</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Darmstadt</t>
+          <t>London</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>london</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>England</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49.87167</t>
+          <t>GO – geographischer Ort &gt; England</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8.65027</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2938913/darmstadt.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>51.50853</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-0.12574</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2973</t>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2643743/london.html</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q84</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>https://www.manchesterjewishstudies.org/moses-gaster-projects</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>https://encyclopedia.yivo.org/article/959.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Treblinka (Vernichtungslager)</t>
+          <t>Löberstraße 20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>treblinka vernichtungslager</t>
+          <t>20 löberstraße</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>52.6451</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22.06891</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/756807/treblinka.html</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>50.5805652</v>
+      </c>
+      <c r="G41" t="n">
+        <v>8.674594600000001</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q152010</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gießen Marktplatz 15</t>
+          <t>Marktplatz 11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15 gießen marktplatz</t>
+          <t>11 marktplatz</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gießen</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>50.58727</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8.67554</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>50.5863583</v>
+      </c>
+      <c r="G42" t="n">
+        <v>8.674898499999999</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2920512</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/Erleben/Über-Gießen/Stolpersteine/Marktplatz-15</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Stolperstein_Gießen_Marktplatz_15_Esther_Stern.JPG</t>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sennfeld (Adelsheim)</t>
+          <t>Marseille</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>adelsheim sennfeld</t>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>49.38014</t>
+          <t>GO – geographischer Ort &gt; Frankreich</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9.38284</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2833011/sennfeld.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>43.29695</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.38107</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q14531586</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2995469</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q23482</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>aus Gießen nach Palästina</t>
+          <t>Niederlande</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>aus gießen nach palästina</t>
+          <t>niederlande</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gießen</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>https://atom.lib.uct.ac.za/uploads/r/university-of-cape-town-libraries-special-collections/a/3/c/a3cc8572f727d61327e4f929a86fc91c339c13cc41721aa18c8f158e13678891/mss_sahgf_schragenheim_publications_025_1-20.pdf</t>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>52.2434979</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.6343227</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>reise_zurueck</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gießen Schillerschule (Volksschule)</t>
+          <t>Oberhessen</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>gießen schillerschule volksschule</t>
+          <t>oberhessen</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Gießen</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2967.1&amp;object=tx%2C2874.2967.1</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Datei:Stolperstein_Gießen_Nordanlage_Esther_Stern.JPG</t>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>50.5833</v>
+      </c>
+      <c r="G45" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15837262</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Esther-Stern-Platz Gießen</t>
+          <t>Palästina</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>esthersternplatz gießen</t>
+          <t>palästina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gießen</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>https://www.lotta-magazin.de/ausgabe/1/den-ermordeten-menschen-ein-gesicht-geben/</t>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>31.6539</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.1035</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/12047392/palestine.html</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q193714</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Elberfeld</t>
+          <t>Posen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>elberfeld</t>
+          <t>posen</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Poznan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>51.10286</t>
+          <t>GO – geographischer Ort &gt; Polska &gt; województwo wielkopolskie &gt; Poznań</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>17.03006</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/3081368/wroclaw.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>52.40692</v>
+      </c>
+      <c r="G47" t="n">
+        <v>16.92993</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1799</t>
+          <t>alte heimat</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3088171/poznan.html</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q268</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Breslau</t>
+          <t>Rüdnitz</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>breslau</t>
+          <t>rüdnitz</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>51.10286</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Brandenburg</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>17.03006</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/3081368</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>https://cja.huji.ac.il/hmm/browser.php?mode=set&amp;id=58391</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>52.7213</v>
+      </c>
+      <c r="G48" t="n">
+        <v>13.625</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>alte_heimat 
+transit</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2843368/ruednitz.html</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q569568</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>https://hachschara.juedische-geschichte-online.net/ueber/hachschara</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>https://www.jewish-places.de/de/DE-MUS-975919Z/facility/2a436a9f-1ad7-4e74-9f48-51946369ecb6/Hachschara---Lager-R%C3%BCdnitz</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Singapur</t>
+          <t>Sachsenhausen</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>singapur</t>
+          <t>sachsenhausen</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Oranienburg</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.36667</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Berlin &gt; Oranienburg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>103.8</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>transit</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/1880251/republic-of-singapore.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>52.766</v>
+      </c>
+      <c r="G49" t="n">
+        <v>13.264</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q334</t>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2925534</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q154498</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>https://www.sachsenhausen-sbg.de/geschichte/1936-1945-konzentrationslager-sachsenhausen/</t>
+        </is>
+      </c>
+      <c r="BN49" t="inlineStr">
+        <is>
+          <t>https://www.orte-der-erinnerung.de/informationen/das-konzentrationslager-sachsenhausen-1936-1945-ereignisse-und-entwicklungen/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bombay</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bombay</t>
+          <t>salzburg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Osterreich</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.07283</t>
+          <t>GO – geographischer Ort &gt; Österreich</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>72.88261</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>47.8137</v>
+      </c>
+      <c r="G50" t="n">
+        <v>13.0451</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t>verkehrsmittel</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/1275339/mumbai.html</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1156</t>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6930925/salzburg-hauptbahnhof.html</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q694694</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Palästina</t>
+          <t>Schlesien</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>palästina</t>
+          <t>schlesien</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>31.65393</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>35.10352</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/12047392/palestine.html</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>50.9206028</v>
+      </c>
+      <c r="G51" t="n">
+        <v>16.4946351</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q193714</t>
+          <t>alte_heimat</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Barmen</t>
+          <t>Sennfeld (Adelsheim)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>barmen</t>
+          <t>adelsheim sennfeld</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Sennfeld</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>51.27737</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen &gt; Sennfeld</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7.19802</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>49.4014</v>
+      </c>
+      <c r="G52" t="n">
+        <v>9.402200000000001</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t>alte_heimat</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2952539/barmen.html</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q153974</t>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2833011/sennfeld.html</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q14531586</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Genua</t>
+          <t>Singapur</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>genua</t>
+          <t>singapur</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>44.40478</t>
+          <t>GO – geographischer Ort &gt; Singapore &gt; Singapore</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>8.94439</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/3176219/genoa.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1.36667</v>
+      </c>
+      <c r="G53" t="n">
+        <v>103.8</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1449</t>
+          <t>transit</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/1880251/republic-of-singapore.html</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q334</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Steinstraße 19,</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>frankreich</t>
+          <t>19 steinstraße</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>reise_zurueck</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/3017382/republic-of-france.html</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>50.5894211</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.671178899999999</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q142</t>
+          <t>alte_heimat</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>jerusalem</t>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>31.76904</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.21633</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/281184</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/en/archives/NNL_CAHJP997013170218605171/NLI</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>https://jewishvirtuallibrary.org/jsource/judaica/ejud_0002_0020_0_20210.html</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>https://www.duden.de/rechtschreibung/Restitution</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>48.7758</v>
+      </c>
+      <c r="G55" t="n">
+        <v>9.1829</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2825297/stuttgart.html</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1022</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Buchenwald</t>
+          <t>Synagoge am Börneplatz, Frankfurt/M</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>buchenwald</t>
+          <t>am börneplatz frankfurtm synagoge</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>50.90302</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>10.07587</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/13665267/aussenlager-abteroda-konzentrationslager-buchenwald.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>50.11035</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.671849999999999</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q152802</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>https://www.buchenwald.de/</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6553153</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q111620976</t>
         </is>
       </c>
     </row>
@@ -2438,596 +3526,651 @@
           <t>aviv tel</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>32.08088</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>34.78057</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>32.0808</v>
+      </c>
+      <c r="G57" t="n">
+        <v>34.7805</v>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t>neue_heimat</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>https://www.geonames.org/293397/tel-aviv.html</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q33935</t>
         </is>
       </c>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>https://prabook.com/web/paul.alsberg/570050</t>
+        </is>
+      </c>
+      <c r="BE57" t="inlineStr">
+        <is>
+          <t>https://irgun-jeckes.org/english/</t>
+        </is>
+      </c>
+      <c r="BF57" t="inlineStr">
+        <is>
+          <t>https://cris.tau.ac.il/en/organisations/the-chaim-weizmann-institute-for-the-study-of-zionism-and-israel-2/</t>
+        </is>
+      </c>
+      <c r="BG57" t="inlineStr">
+        <is>
+          <t>https://en.jabotinsky.org/</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Theresienstadt</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>theresienstadt</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Tschechoslowakei</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Tschechoslowakei</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>50.5136</v>
+      </c>
+      <c r="G58" t="n">
+        <v>14.1497</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/12217751/theresienstadt-concentration-camp-and-ghetto.html</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q160175</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Wuppertal</t>
+          <t>Treblinka (Vernichtungslager)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>wuppertal</t>
+          <t>treblinka vernichtungslager</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Wolka Okraglik</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>51.25627</t>
+          <t>GO – geographischer Ort &gt; Polska &gt; województwo mazowieckie &gt; gmina Kosów Lacki &gt; Wólka Okrąglik</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>7.14816</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2805753/wuppertal.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>52.6303</v>
+      </c>
+      <c r="G59" t="n">
+        <v>22.0492</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2107</t>
-        </is>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
-        </is>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>https://alte-synagoge-wuppertal.de/fileadmin/user_upload/BAS_Gedenkstaetten_Wuppertal-7.pdf</t>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/756807/treblinka.html</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q152010</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Association of Israelis of Central European Origin (AICEO) </t>
+          <t>Triest</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>aiceo association central european israelis of origin</t>
+          <t>triest</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Trieste</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Italia &gt; Friuli-Venezia Giulia &gt; Trieste</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>45.6364</v>
+      </c>
+      <c r="G60" t="n">
+        <v>13.774</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/9796929/porto-di-trieste.html</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1567848</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digitales Archiv vom Else-Lasker-Schüler-Gesellschaft </t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>archiv digitales elselaskerschülergesellschaft vom</t>
+          <t>states united</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; USA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>39</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-98</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6252001/united-states.html</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Walltorstraße 48</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>israel</t>
+          <t>48 walltorstraße</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>34.75</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/294640/state-of-israel.html</t>
-        </is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>50.5895607</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.6775827</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q801</t>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2920512</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Frankfurt an der Oder</t>
+          <t>Wien</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>an der frankfurt oder</t>
+          <t>wien</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Osterreich</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>52.33694</t>
+          <t>GO – geographischer Ort &gt; Österreich</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>14.49222</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2925534</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q154498</t>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="G63" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1741</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rüdnitz</t>
+          <t>Wullenweberstraße 11, Berlin-Moabit</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>rüdnitz</t>
+          <t>11 berlinmoabit wullenweberstraße</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>52.72137</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Berlin</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13.62502</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>alte_heimat 
-transit</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2843368/ruednitz.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>52.523</v>
+      </c>
+      <c r="G64" t="n">
+        <v>13.3415</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q569568</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>https://hachschara.juedische-geschichte-online.net/ueber/hachschara</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>https://www.jewish-places.de/de/DE-MUS-975919Z/facility/2a436a9f-1ad7-4e74-9f48-51946369ecb6/Hachschara---Lager-R%C3%BCdnitz</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2950159</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q56161165</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>https://www.stolpersteine-berlin.de/de/wullenweberstr/11/auguste-stern</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Wuppertal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>salzburg</t>
+          <t>wuppertal</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>47.81373</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13.04515</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6930925/salzburg-hauptbahnhof.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>51.2562</v>
+      </c>
+      <c r="G65" t="n">
+        <v>7.1481</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q694694</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2805753/wuppertal.html</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2107</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>https://alte-synagoge-wuppertal.de/fileadmin/user_upload/BAS_Gedenkstaetten_Wuppertal-7.pdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Triest</t>
+          <t>Wölfersheim</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>triest</t>
+          <t>wölfersheim</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>45.63647</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13.774</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/9796929/porto-di-trieste.html</t>
-        </is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.816700000000001</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1567848</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2806852/woelfersheim.html</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q634098</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ben Shemen  - Kinderdorf</t>
+          <t>Yad Vashem</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ben kinderdorf shemen</t>
+          <t>vashem yad</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>31.959019444444</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Jerusalem</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>34.927830555556</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>neue_heimat
-Ort der Zeit</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/maps/google_31.959_34.9278.html</t>
-        </is>
+          <t>wikidata</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>31.7744237</v>
+      </c>
+      <c r="G67" t="n">
+        <v>35.1772481</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2777009</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Kinder-_und_Jugenddorf_Ben_Shemen</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>https://www.ben-shemen.org.il/en</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q156591</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>https://collections.yadvashem.org/en/names/13219727</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>Zypern</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>kibbuz</t>
+          <t>zypern</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Kannavia</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Κύπρος - Kıbrıs &gt; Κύπρος &gt; Καννάβια &gt; Kannavia</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>35</v>
+      </c>
+      <c r="G68" t="n">
+        <v>33</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/146669/republic-of-cyprus.html</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q229</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>https://encyclopedia.ushmm.org/content/en/article/cyprus-detention-camps</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Zypern</t>
+          <t>Ēmeq Yizrəʿēl</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>zypern</t>
+          <t>yizrəʿēl ēmeq</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Emek (Jesreelebene)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Emek (Jesreelebene)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/146669/republic-of-cyprus.html</t>
-        </is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>32.60417</v>
+      </c>
+      <c r="G69" t="n">
+        <v>35.23639</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q229</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.ushmm.org/content/en/article/cyprus-detention-camps</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Posen</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>posen</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>52.40692</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>16.92993</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>alte heimat</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/3088171/poznan.html</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q268</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Sachsenhausen</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>sachsenhausen</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>52.33694</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>14.49222</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2925534</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>https://www.sachsenhausen-sbg.de/geschichte/1936-1945-konzentrationslager-sachsenhausen/</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>london</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>51.50853</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-0.12574</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2643743/london.html</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q84</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>https://www.manchesterjewishstudies.org/moses-gaster-projects</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959</t>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293165/jezreel-valley.html</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q763829</t>
         </is>
       </c>
     </row>

--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -1113,12 +1113,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; India &gt; Maharashtra &gt; Mumbai</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Campello sul Clitunno</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Italia &gt; Umbria &gt; Campello sul Clitunno</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kehl</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Kehl</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ein HaNetziv</t>
+          <t>Kibbuz</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz &gt; Ein HaNetziv</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kibbuz Rodges</t>
+          <t>Kibbuz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz &gt; Kibbuz Rodges</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2476,12 +2476,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tirat Tsvi</t>
+          <t>Kibbuz</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz &gt; Tirat Tsvi</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poznan</t>
+          <t>Polen</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Polska &gt; województwo wielkopolskie &gt; Poznań</t>
+          <t>GO – geographischer Ort &gt; Polen</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sennfeld</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen &gt; Sennfeld</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Singapore &gt; Singapore</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wolka Okraglik</t>
+          <t>Polen</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Polska &gt; województwo mazowieckie &gt; gmina Kosów Lacki &gt; Wólka Okrąglik</t>
+          <t>GO – geographischer Ort &gt; Polen</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>50.5895607</v>
+        <v>50.589967</v>
       </c>
       <c r="G62" t="n">
-        <v>8.6775827</v>
+        <v>8.6783959</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -4086,12 +4086,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kannavia</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Κύπρος - Kıbrıs &gt; Κύπρος &gt; Καννάβια &gt; Kannavia</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">

--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN69"/>
+  <dimension ref="A1:BU86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,86 +747,121 @@
           <t>www.orte-der-erinnerung.de</t>
         </is>
       </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>www.luckenwalde.de</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>share.google</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>frgym.de</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>ns.gis-bldam-brandenburg.de</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>www.ernst-abbe.de</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>www.archeu.unifi.it</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>vimeo.com</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bahnhof, Frankfurt am Main</t>
+          <t>Aachen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>am bahnhof frankfurt main</t>
+          <t>aachen</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>50.11035</v>
+        <v>50.7766</v>
       </c>
       <c r="G2" t="n">
-        <v>8.671849999999999</v>
+        <v>6.0834</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>verkehrsmittel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/6553153</t>
+          <t>https://www.geonames.org/3247449</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1794</t>
+          <t>https://www.wikidata.org/wiki/Q1017</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Baiertal</t>
+          <t>Bahnhof, Frankfurt am Main</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>baiertal</t>
+          <t>am bahnhof frankfurt main</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>49.2944</v>
+        <v>50.11035</v>
       </c>
       <c r="G3" t="n">
-        <v>8.7889</v>
+        <v>8.671849999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -835,24 +870,24 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2953189/baiertal.html</t>
+          <t>https://www.geonames.org/6553153</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q7904</t>
+          <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Barmen</t>
+          <t>Baiertal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>barmen</t>
+          <t>baiertal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -871,10 +906,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>51.2773</v>
+        <v>49.2944</v>
       </c>
       <c r="G4" t="n">
-        <v>7.198</v>
+        <v>8.7889</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -883,290 +918,275 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2952539/barmen.html</t>
+          <t>https://www.geonames.org/2953189/baiertal.html</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q153974</t>
+          <t>https://www.wikidata.org/wiki/Q7904</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belgien</t>
+          <t>Barmen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>belgien</t>
+          <t>barmen</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50.6402809</v>
+        <v>51.2773</v>
       </c>
       <c r="G5" t="n">
-        <v>4.6667145</v>
+        <v>7.198</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2952539/barmen.html</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q153974</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Bat Yam</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bat yam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>32.0237</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34.7518</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/295548</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q208725</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Belgien</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>belgien</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>50.6402809</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.6667145</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Ben Shemen  - Kinderdorf</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ben kinderdorf shemen</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ben Shemen</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Ben Shemen</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>31.959</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G8" t="n">
         <v>34.9278</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>neue_heimat
 Ort der Zeit</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://www.geonames.org/maps/google_31.959_34.9278.html</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q2777009</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>https://de.wikipedia.org/wiki/Kinder-_und_Jugenddorf_Ben_Shemen</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>https://www.ben-shemen.org.il/en</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Berdytschiw</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>berdytschiw</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Russland / Ukraine &gt; Ukraine</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>49.8989</v>
-      </c>
-      <c r="G7" t="n">
-        <v>28.6011</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/712441/berdychiv.html</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q7904</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>berlin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>52.5034</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13.3815</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2950159/berlin.html</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q64</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Stern%E2%80%99sches_Konservatorium</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>https://www.gedenktafeln-in-berlin.de/gedenktafeln/detail/juedische-private-musikschule-hollaender/1040</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>https://adassjisroel.de/gestern/schulwerk-der-adass-jisroel/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bombay</t>
+          <t>Berdytschiw</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>bombay</t>
+          <t>berdytschiw</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Russland / Ukraine &gt; Ukraine</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>19.07283</v>
+        <v>49.8989</v>
       </c>
       <c r="G9" t="n">
-        <v>72.88261</v>
+        <v>28.6011</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>verkehrsmittel</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/1275339/mumbai.html</t>
+          <t>https://www.geonames.org/712441/berdychiv.html</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1156</t>
+          <t>https://www.wikidata.org/wiki/Q7904</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Breidenbach</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>breidenbach</t>
+          <t>berlin</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1175,58 +1195,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50.8722</v>
+        <v>52.5243</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4053</v>
+        <v>13.4105</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>erinnerungsort</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2944820/breidenbach.html</t>
+          <t>https://www.geonames.org/2950159/berlin.html</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q564579</t>
+          <t>https://www.wikidata.org/wiki/Q64</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Stern%E2%80%99sches_Konservatorium</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>https://www.gedenktafeln-in-berlin.de/gedenktafeln/detail/juedische-private-musikschule-hollaender/1040</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>https://adassjisroel.de/gestern/schulwerk-der-adass-jisroel/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Breslau</t>
+          <t>Bernstein, Neumark</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>breslau</t>
+          <t>bernstein neumark</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Schlesien</t>
+          <t>Bern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Schlesien</t>
+          <t>GO – geographischer Ort &gt; Schweiz &gt; Bern</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>51.1028</v>
+        <v>53.04354</v>
       </c>
       <c r="G11" t="n">
-        <v>17.03</v>
+        <v>15.30447</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1235,92 +1270,82 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/3081368</t>
+          <t>https://www.geonames.org/3089286</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1799</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>https://cja.huji.ac.il/hmm/browser.php?mode=set&amp;id=58391</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>https://www.buchenwald.de/</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>https://www.gedenktafeln-in-berlin.de/gedenktafeln/detail/haus-der-zionistischen-organisationen/1012</t>
+          <t>https://www.wikidata.org/wiki/Q989441</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brücke Kehl–Straßburg (Rheinquerung)</t>
+          <t>Bombay</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>brücke kehlstraßburg rheinquerung</t>
+          <t>bombay</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kehl</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Kehl</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>wikidata</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>48.5737</v>
+        <v>19.07283</v>
       </c>
       <c r="G12" t="n">
-        <v>7.80194</v>
+        <v>72.88261</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>verkehrsmittel</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/1275339/mumbai.html</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1375288</t>
+          <t>https://www.wikidata.org/wiki/Q1156</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Buchenwald</t>
+          <t>Breidenbach</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>buchenwald</t>
+          <t>breidenbach</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1329,51 +1354,46 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50.903</v>
+        <v>50.8722</v>
       </c>
       <c r="G13" t="n">
-        <v>10.0758</v>
+        <v>8.4053</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>ort_der_zeit</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/13665267/aussenlager-abteroda-konzentrationslager-buchenwald.html</t>
+          <t>https://www.geonames.org/2944820/breidenbach.html</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q152802</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>https://www.buchenwald.de/</t>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Darmstadt</t>
+          <t>Breslau</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>darmstadt</t>
+          <t>breslau</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Schlesien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Schlesien</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1382,84 +1402,94 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>49.8728</v>
+        <v>51.1028</v>
       </c>
       <c r="G14" t="n">
-        <v>8.651199999999999</v>
+        <v>17.03</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>verkehrsmittel</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2938913/darmstadt.html</t>
+          <t>https://www.geonames.org/3081368</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2973</t>
+          <t>https://www.wikidata.org/wiki/Q1799</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>https://cja.huji.ac.il/hmm/browser.php?mode=set&amp;id=58391</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>https://www.buchenwald.de/</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>https://www.gedenktafeln-in-berlin.de/gedenktafeln/detail/haus-der-zionistischen-organisationen/1012</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Brücke Kehl–Straßburg (Rheinquerung)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deutschland</t>
+          <t>brücke kehlstraßburg rheinquerung</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Kehl</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Kehl</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>wikidata</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>51.5</v>
+        <v>48.5737</v>
       </c>
       <c r="G15" t="n">
-        <v>10.5</v>
+        <v>7.80194</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2921044/federal-republic-of-germany.html</t>
+          <t>verkehrsmittel</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q183</t>
+          <t>https://www.wikidata.org/wiki/Q1375288</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elberfeld</t>
+          <t>Buchenwald</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>elberfeld</t>
+          <t>buchenwald</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1478,124 +1508,99 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>51.2508</v>
+        <v>50.903</v>
       </c>
       <c r="G16" t="n">
-        <v>7.1481</v>
+        <v>10.0758</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>ort_der_zeit</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/3081368/wroclaw.html</t>
+          <t>https://www.geonames.org/13665267/aussenlager-abteroda-konzentrationslager-buchenwald.html</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1799</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Kameraden,_deutsch-j%C3%BCdischer_Wanderbund</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>https://hachschara.juedische-geschichte-online.net/en/organization/gnd/10090732-5</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>https://carl-fuhlrott-gymnasium.de/</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>https://www.wuppertal.de/denkmalliste-online/Detail/Show/2218</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>https://herder-schule.de/schulgeschichte/</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>https://www.juedisches-europa.net/archiv-seite-4-1/3-2019/j%C3%BCdische-jugendbewegung/</t>
+          <t>https://www.wikidata.org/wiki/Q152802</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>https://www.buchenwald.de/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Esther-Stern-Platz Gießen</t>
+          <t>Darmstadt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>esthersternplatz gießen</t>
+          <t>darmstadt</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>50.5862066</v>
+        <v>49.8728</v>
       </c>
       <c r="G17" t="n">
-        <v>8.6742306</v>
+        <v>8.651199999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>https://www.lotta-magazin.de/ausgabe/1/den-ermordeten-menschen-ein-gesicht-geben/</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2938913/darmstadt.html</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2973</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Frankfurt (Main) Hauptbahnhof</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>frankfurt hauptbahnhof main</t>
+          <t>deutschland</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1604,58 +1609,68 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>50.1042</v>
+        <v>51.5</v>
       </c>
       <c r="G18" t="n">
-        <v>8.657500000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>reise_zurueck</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/6290300/frankfurt-hauptbahnhof.html</t>
+          <t>https://www.geonames.org/2921044/federal-republic-of-germany.html</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q165368</t>
+          <t>https://www.wikidata.org/wiki/Q183</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Kartell_J%C3%BCdischer_Verbindungen</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>http://www.zionistarchives.org.il/en/AttheCZA/Pages/BlauWeiss.aspx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frankfurt an der Oder</t>
+          <t>Drezdenko</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>an der frankfurt oder</t>
+          <t>drezdenko</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brandenburg</t>
+          <t>Polen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Brandenburg</t>
+          <t>GO – geographischer Ort &gt; Polen</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>52.3471</v>
+        <v>52.83831</v>
       </c>
       <c r="G19" t="n">
-        <v>14.5506</v>
+        <v>15.83079</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1664,79 +1679,34 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2925534</t>
+          <t>https://www.geonames.org/3100127</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q154498</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Kameraden,_deutsch-j%C3%BCdischer_Wanderbund</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>https://www.juedisches-europa.net/archiv-seite-4-1/3-2019/j%C3%BCdische-jugendbewegung/</t>
-        </is>
-      </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>http://www.zionistarchives.org.il/en/familyresearch/GenealogyDatabases/Pages/YouthImmigration.aspx</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>https://www.liebknecht-gymnasium.de/schulprofil/zur-geschichte-der-schule.html</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>https://www.dhm.de/lemo/kapitel/ns-regime/ns-organisationen/bund-deutscher-maedel</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>https://www.gdw-berlin.de/vertiefung/themen/13-widerstand-von-jugendlichen</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>https://kiju-aliyah.de/historie/</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>https://youthaliyah.org.uk/about#history</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>https://www.frankfurt-oder-juedisch.de/homepage/menschen/dr-hermann-neumark/</t>
+          <t>https://www.wikidata.org/wiki/Q836961</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Frankfurt/M</t>
+          <t>Elberfeld</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>frankfurtm</t>
+          <t>elberfeld</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Frankfurt am Main</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1745,10 +1715,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>50.11</v>
+        <v>51.2508</v>
       </c>
       <c r="G20" t="n">
-        <v>8.68</v>
+        <v>7.1481</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1757,82 +1727,112 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
+          <t>https://www.geonames.org/3081368/wroclaw.html</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1794</t>
+          <t>https://www.wikidata.org/wiki/Q1799</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Kameraden,_deutsch-j%C3%BCdischer_Wanderbund</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>https://hachschara.juedische-geschichte-online.net/en/organization/gnd/10090732-5</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>https://carl-fuhlrott-gymnasium.de/</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>https://www.wuppertal.de/denkmalliste-online/Detail/Show/2218</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>https://herder-schule.de/schulgeschichte/</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>https://www.juedisches-europa.net/archiv-seite-4-1/3-2019/j%C3%BCdische-jugendbewegung/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Esther-Stern-Platz Gießen</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>frankreich</t>
+          <t>esthersternplatz gießen</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>nominatim</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>50.5862066</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>8.6742306</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/3017382/republic-of-france.html</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q142</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://www.lotta-magazin.de/ausgabe/1/den-ermordeten-menschen-ein-gesicht-geben/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Genua</t>
+          <t>Florenz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>genua</t>
+          <t>florenz</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Genova</t>
+          <t>Firenze</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Italia &gt; Liguria &gt; Genova</t>
+          <t>GO – geographischer Ort &gt; Italia &gt; Toscana &gt; Cascine del Riccio &gt; Firenze</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1841,46 +1841,56 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>44.4047</v>
+        <v>43.7465</v>
       </c>
       <c r="G22" t="n">
-        <v>8.9443</v>
+        <v>11.2583</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>verkehrsmittel</t>
+          <t>transit,verkehrsmittel</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/3176219/genoa.html</t>
+          <t>https://www.geonames.org/3182917</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1449</t>
+          <t>https://www.wikidata.org/wiki/Q4012410</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Landschulheim_Florenz</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>https://www.archeu.unifi.it/vp-534--gli-intellettuali-ebrei-tedeschi-a-firenze-tra-il-1933-e-il-1938.html#</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gießen</t>
+          <t>Frankfurt (Main) Hauptbahnhof</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gießen</t>
+          <t>frankfurt hauptbahnhof main</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1889,169 +1899,199 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>50.5849</v>
+        <v>50.1042</v>
       </c>
       <c r="G23" t="n">
-        <v>8.6724</v>
+        <v>8.657500000000001</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ort_der_zeit</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2938913/darmstadt.html</t>
+          <t>https://www.geonames.org/6290300/frankfurt-hauptbahnhof.html</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2973</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1</t>
+          <t>https://www.wikidata.org/wiki/Q165368</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gießen Marktplatz 15</t>
+          <t>Frankfurt an der Oder</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15 gießen marktplatz</t>
+          <t>an der frankfurt oder</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Brandenburg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Brandenburg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>50.58727</v>
+        <v>52.3471</v>
       </c>
       <c r="G24" t="n">
-        <v>8.67554</v>
+        <v>14.5506</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>erinnerungsort</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2920512</t>
+          <t>https://www.geonames.org/2925534</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q564579</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/Erleben/Über-Gießen/Stolpersteine/Marktplatz-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Stolperstein_Gießen_Marktplatz_15_Esther_Stern.JPG</t>
+          <t>https://www.wikidata.org/wiki/Q154498</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Kameraden,_deutsch-j%C3%BCdischer_Wanderbund</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>https://www.juedisches-europa.net/archiv-seite-4-1/3-2019/j%C3%BCdische-jugendbewegung/</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>http://www.zionistarchives.org.il/en/familyresearch/GenealogyDatabases/Pages/YouthImmigration.aspx</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>https://www.liebknecht-gymnasium.de/schulprofil/zur-geschichte-der-schule.html</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>https://www.dhm.de/lemo/kapitel/ns-regime/ns-organisationen/bund-deutscher-maedel</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>https://www.gdw-berlin.de/vertiefung/themen/13-widerstand-von-jugendlichen</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>https://kiju-aliyah.de/historie/</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>https://youthaliyah.org.uk/about#history</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>https://www.frankfurt-oder-juedisch.de/homepage/menschen/dr-hermann-neumark/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gießen Schillerschule (Volksschule)</t>
+          <t>Frankfurt/M</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gießen schillerschule volksschule</t>
+          <t>frankfurtm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Frankfurt am Main</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>50.5898867</v>
+        <v>50.11</v>
       </c>
       <c r="G25" t="n">
-        <v>8.6748519</v>
+        <v>8.68</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>alte_heimat</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2967.1&amp;object=tx%2C2874.2967.1</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>https://de.wikipedia.org/wiki/Datei:Stolperstein_Gießen_Nordanlage_Esther_Stern.JPG</t>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6553153/frankfurt-am-main.html</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1794</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Großen-Linden</t>
+          <t>Frankreich</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>großenlinden</t>
+          <t>frankreich</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>50.52785</v>
+        <v>46</v>
       </c>
       <c r="G26" t="n">
-        <v>8.662000000000001</v>
+        <v>2</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2060,34 +2100,34 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/11974166/grossen-linden.html</t>
+          <t>https://www.geonames.org/3017382/republic-of-france.html</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q116016915</t>
+          <t>https://www.wikidata.org/wiki/Q142</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>haifa</t>
+          <t>freiburg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palastina - Israel</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2096,84 +2136,94 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>32.5833</v>
+        <v>47.9959</v>
       </c>
       <c r="G27" t="n">
-        <v>35</v>
+        <v>7.8522</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>neue_heimat</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/294800/haifa.html</t>
+          <t>https://www.geonames.org/2925177</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q185845</t>
+          <t>https://www.wikidata.org/wiki/Q2833</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Haifa, Universität, Bibliothek</t>
+          <t>Genua</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bibliothek haifa universität</t>
+          <t>genua</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Genova</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Haifa</t>
+          <t>GO – geographischer Ort &gt; Italia &gt; Liguria &gt; Genova</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>32.8191218</v>
+        <v>44.4047</v>
       </c>
       <c r="G28" t="n">
-        <v>34.9983856</v>
+        <v>8.9443</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>neue_heimat</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3176219/genoa.html</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1449</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Italien</t>
+          <t>Gießen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>italien</t>
+          <t>gießen</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2182,232 +2232,217 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>42.8333</v>
+        <v>50.5849</v>
       </c>
       <c r="G29" t="n">
-        <v>12.8333</v>
+        <v>8.6724</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
+          <t>ort_der_zeit</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/3175395</t>
+          <t>https://www.geonames.org/2938913/darmstadt.html</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q38</t>
+          <t>https://www.wikidata.org/wiki/Q2973</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Gießen Marktplatz 15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>jerusalem</t>
+          <t>15 gießen marktplatz</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palastina - Israel</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>31.769</v>
+        <v>50.58727</v>
       </c>
       <c r="G30" t="n">
-        <v>35.2163</v>
+        <v>8.67554</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>neue_heimat</t>
+          <t>erinnerungsort</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/281184</t>
+          <t>https://www.geonames.org/2920512</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1218</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>https://www.nli.org.il/en/archives/NNL_CAHJP997013170218605171/NLI</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>https://jewishvirtuallibrary.org/jsource/judaica/ejud_0002_0020_0_20210.html</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>https://www.duden.de/rechtschreibung/Restitution</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>https://en.huji.ac.il/</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>http://www.zionistarchives.org.il/en/pages/default.aspx</t>
-        </is>
-      </c>
-      <c r="BA30" t="inlineStr">
-        <is>
-          <t>https://www.archives.gov.il/</t>
-        </is>
-      </c>
-      <c r="BB30" t="inlineStr">
-        <is>
-          <t>https://www.lbi.org/about/lbi-international/</t>
-        </is>
-      </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>https://www.yadvashem.org/de/about/yad-vashem.html</t>
-        </is>
-      </c>
-      <c r="BD30" t="inlineStr">
-        <is>
-          <t>https://prabook.com/web/paul.alsberg/570050</t>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/Erleben/Über-Gießen/Stolpersteine/Marktplatz-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Stolperstein_Gießen_Marktplatz_15_Esther_Stern.JPG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kehl am Rhein</t>
+          <t>Gießen Schillerschule (Volksschule)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>am kehl rhein</t>
+          <t>gießen schillerschule volksschule</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>nominatim</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>48.57297</v>
+        <v>50.5898867</v>
       </c>
       <c r="G31" t="n">
-        <v>7.81523</v>
+        <v>8.6748519</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2891951/kehl.html</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q15979</t>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2967.1&amp;object=tx%2C2874.2967.1</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Datei:Stolperstein_Gießen_Nordanlage_Esther_Stern.JPG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>Großen-Linden</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kibbuz</t>
+          <t>großenlinden</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palastina - Israel</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>31.9522788</v>
+        <v>50.52785</v>
       </c>
       <c r="G32" t="n">
-        <v>34.921944</v>
+        <v>8.662000000000001</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/11974166/grossen-linden.html</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q116016915</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kibbuz Ein HaNetziv</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ein hanetziv kibbuz</t>
+          <t>haifa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>32.4715</v>
+        <v>32.5833</v>
       </c>
       <c r="G33" t="n">
-        <v>35.50014</v>
+        <v>35</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2416,34 +2451,34 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/295211/-en-hanaziv.html</t>
+          <t>https://www.geonames.org/294800/haifa.html</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2095906</t>
+          <t>https://www.wikidata.org/wiki/Q185845</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kibbuz Rodges, besteht nicht mehr (in der Nähe von Petah Tikva)</t>
+          <t>Haifa, Universität, Bibliothek</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>besteht der in kibbuz mehr nicht nähe petah rodges tikva von</t>
+          <t>bibliothek haifa universität</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Haifa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2452,10 +2487,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>32.0877639</v>
+        <v>32.8191218</v>
       </c>
       <c r="G34" t="n">
-        <v>34.8859985</v>
+        <v>34.9983856</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2466,262 +2501,302 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kibbuz Tirat Tsvi</t>
+          <t>Italien</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kibbuz tirat tsvi</t>
+          <t>italien</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kibbuz</t>
+          <t>GO - geographischer Ort</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Kibbuz</t>
+          <t>GO – geographischer Ort</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>32.42131</v>
+        <v>42.8333</v>
       </c>
       <c r="G35" t="n">
-        <v>35.52791</v>
+        <v>12.8333</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>neue_heimat</t>
+          <t>reise_zurueck</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/293304/tirat-tsvi.html</t>
+          <t>https://www.geonames.org/3175395</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q550025</t>
+          <t>https://www.wikidata.org/wiki/Q38</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Abessinienkrieg</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Klein-Linden</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kleinlinden</t>
+          <t>jerusalem</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>50.55685</v>
+        <v>31.769</v>
       </c>
       <c r="G36" t="n">
-        <v>8.647119999999999</v>
+        <v>35.2163</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
+          <t>neue_heimat</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2888549/klein-linden.html</t>
+          <t>https://www.geonames.org/281184</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q1571834</t>
+          <t>https://www.wikidata.org/wiki/Q1218</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Heinz_Guttfeld</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>https://www.nli.org.il/en/archives/NNL_CAHJP997013170218605171/NLI</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>https://jewishvirtuallibrary.org/jsource/judaica/ejud_0002_0020_0_20210.html</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>https://www.duden.de/rechtschreibung/Restitution</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>https://en.huji.ac.il/</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>http://www.zionistarchives.org.il/en/pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>https://www.archives.gov.il/</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.lbi.org/about/lbi-international/</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>https://www.yadvashem.org/de/about/yad-vashem.html</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>https://prabook.com/web/paul.alsberg/570050</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Koblenz</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>koblenz</t>
+          <t>kathmandu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Koblenz</t>
+          <t>kaatthmaaddauN mhaangrpaalikaa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Koblenz</t>
+          <t>GO – geographischer Ort &gt; नेपाल &gt; बागमती प्रदेश &gt; काठमाडौँ महानगरपालिका</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>wikidata</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>53.2525</v>
+        <v>27.7016</v>
       </c>
       <c r="G37" t="n">
-        <v>10.414444444444</v>
+        <v>85.3206</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>erinnerungsort</t>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/1283240</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q3920</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>https://apps.bundesarchiv.de/gedenkbuch/de976422</t>
+          <t>https://www.wikidata.org/wiki/Q3037</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KZ Buchenwald</t>
+          <t>Kehl am Rhein</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>buchenwald kz</t>
+          <t>am kehl rhein</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Buchenwald</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Buchenwald</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>51.0214</v>
+        <v>48.57297</v>
       </c>
       <c r="G38" t="n">
-        <v>11.2486</v>
+        <v>7.81523</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>ort_der_zeit</t>
+          <t>verkehrsmittel</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/8644023/konzentrationslager-buchenwald.html</t>
+          <t>https://www.geonames.org/2891951/kehl.html</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q152802</t>
+          <t>https://www.wikidata.org/wiki/Q15979</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lollar</t>
+          <t>Kibbuz</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>lollar</t>
+          <t>kibbuz</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>nominatim</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>50.65</v>
+        <v>31.9522788</v>
       </c>
       <c r="G39" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6557780</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q625061</t>
-        </is>
+        <v>34.921944</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Kibbuz Ein HaNetziv</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>london</t>
+          <t>ein hanetziv kibbuz</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; England</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2730,56 +2805,46 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>51.50853</v>
+        <v>32.4715</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.12574</v>
+        <v>35.50014</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ort_der_zeit</t>
+          <t>neue_heimat</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2643743/london.html</t>
+          <t>https://www.geonames.org/295211/-en-hanaziv.html</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q84</t>
-        </is>
-      </c>
-      <c r="AQ40" t="inlineStr">
-        <is>
-          <t>https://www.manchesterjewishstudies.org/moses-gaster-projects</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.yivo.org/article/959.</t>
+          <t>https://www.wikidata.org/wiki/Q2095906</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Löberstraße 20</t>
+          <t>Kibbuz Rodges, besteht nicht mehr (in der Nähe von Petah Tikva)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>20 löberstraße</t>
+          <t>besteht der in kibbuz mehr nicht nähe petah rodges tikva von</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2788,94 +2853,84 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>50.5805652</v>
+        <v>32.0877639</v>
       </c>
       <c r="G41" t="n">
-        <v>8.674594600000001</v>
+        <v>34.8859985</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+          <t>neue_heimat</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marktplatz 11</t>
+          <t>Kibbuz Tirat Tsvi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11 marktplatz</t>
+          <t>kibbuz tirat tsvi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Giessen</t>
+          <t>Palastina - Israel</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>50.5863583</v>
+        <v>32.42131</v>
       </c>
       <c r="G42" t="n">
-        <v>8.674898499999999</v>
+        <v>35.52791</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>neue_heimat</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2920512</t>
+          <t>https://www.geonames.org/293304/tirat-tsvi.html</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q564579</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+          <t>https://www.wikidata.org/wiki/Q550025</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Marseille</t>
+          <t>Klein-Linden</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>marseille</t>
+          <t>kleinlinden</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frankreich</t>
+          <t>Giessen</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Frankreich</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2884,84 +2939,94 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>43.29695</v>
+        <v>50.55685</v>
       </c>
       <c r="G43" t="n">
-        <v>5.38107</v>
+        <v>8.647119999999999</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>verkehrsmittel</t>
+          <t>reise_zurueck</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2995469</t>
+          <t>https://www.geonames.org/2888549/klein-linden.html</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q23482</t>
+          <t>https://www.wikidata.org/wiki/Q1571834</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Niederlande</t>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>niederlande</t>
+          <t>koblenz</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Koblenz</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Koblenz</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>nominatim</t>
+          <t>wikidata</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>52.2434979</v>
+        <v>53.2525</v>
       </c>
       <c r="G44" t="n">
-        <v>5.6343227</v>
+        <v>10.414444444444</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>reise_zurueck</t>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q3920</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>https://apps.bundesarchiv.de/gedenkbuch/de976422</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Oberhessen</t>
+          <t>KZ Buchenwald</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>oberhessen</t>
+          <t>buchenwald kz</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Buchenwald</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Buchenwald</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2970,36 +3035,46 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>50.5833</v>
+        <v>51.0214</v>
       </c>
       <c r="G45" t="n">
-        <v>8.75</v>
+        <v>11.2486</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/8644023/konzentrationslager-buchenwald.html</t>
+        </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q15837262</t>
+          <t>https://www.wikidata.org/wiki/Q152802</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Palästina</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>palästina</t>
+          <t>köln</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Palastina - Israel</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3008,41 +3083,36 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>31.6539</v>
+        <v>50.9333</v>
       </c>
       <c r="G46" t="n">
-        <v>35.1035</v>
+        <v>6.95</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>neue_heimat</t>
+          <t>verkehrsmittel</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/12047392/palestine.html</t>
+          <t>https://www.geonames.org/2886242</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q193714</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
+          <t>https://www.wikidata.org/wiki/Q365</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Posen</t>
+          <t>Kętrzyn</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>posen</t>
+          <t>kętrzyn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3057,887 +3127,928 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>geonames</t>
+          <t>chronotopi</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>52.40692</v>
+        <v>54.05</v>
       </c>
       <c r="G47" t="n">
-        <v>16.92993</v>
+        <v>21.4166</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>alte heimat</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/3088171/poznan.html</t>
+          <t>https://www.geonames.org/769275</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q268</t>
+          <t>https://www.wikidata.org/wiki/Q319397</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>Lollar</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>lollar</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="G48" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6557780</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q625061</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>london</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; England</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>51.5085</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.1257</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2643743/london.html</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q84</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>https://www.manchesterjewishstudies.org/moses-gaster-projects</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>https://encyclopedia.yivo.org/article/959.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Luckenwalde</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>luckenwalde</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Brandenburg</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Brandenburg</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>52.0902</v>
+      </c>
+      <c r="G50" t="n">
+        <v>13.1677</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2875484</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q574146</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Luckenwalde</t>
+        </is>
+      </c>
+      <c r="BO50" t="inlineStr">
+        <is>
+          <t>https://www.luckenwalde.de/</t>
+        </is>
+      </c>
+      <c r="BP50" t="inlineStr">
+        <is>
+          <t>https://share.google/711co2KqjTr2bK1sz</t>
+        </is>
+      </c>
+      <c r="BQ50" t="inlineStr">
+        <is>
+          <t>https://frgym.de/schulgeschichte_1.html</t>
+        </is>
+      </c>
+      <c r="BR50" t="inlineStr">
+        <is>
+          <t>https://ns.gis-bldam-brandenburg.de/hida4web/view?docId=obj09105418.xml</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Lydda Airport</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>airport lydda</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Tel Aviv</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>32.0136</v>
+      </c>
+      <c r="G51" t="n">
+        <v>34.8865</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/390285</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q181479</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Löberstraße 20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20 löberstraße</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Giessen</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>50.5805652</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.674594600000001</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Marktplatz 11</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>11 marktplatz</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Giessen</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>50.5863583</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.674898499999999</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2920512</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>marseille</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Frankreich</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Frankreich</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>43.29695</v>
+      </c>
+      <c r="G54" t="n">
+        <v>5.38107</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2995469</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q23482</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>nepal</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>28</v>
+      </c>
+      <c r="G55" t="n">
+        <v>84</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/1282988</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q837</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Neuköllner Kaiser-Friedrich-Realgymnasium
+Berlin</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>berlin kaiserfriedrichrealgymnasium neuköllner</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Realgymnasium</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen &gt; Realgymnasium</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>52.4834</v>
+      </c>
+      <c r="G56" t="n">
+        <v>13.4372</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2864695</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q456397</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Walther_Lehmkuhl</t>
+        </is>
+      </c>
+      <c r="BS56" t="inlineStr">
+        <is>
+          <t>https://www.ernst-abbe.de/schulleben/geschichte-unserer-schule/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>niederlande</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>52.2434979</v>
+      </c>
+      <c r="G57" t="n">
+        <v>5.6343227</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>reise_zurueck</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Oberhessen</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>oberhessen</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>50.5833</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q15837262</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Palästina</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>palästina</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>31.6539</v>
+      </c>
+      <c r="G59" t="n">
+        <v>35.1035</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/12047392/palestine.html</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q193714</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Survey_of_Palestine</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Posen</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>posen</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Polen</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Polen</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>52.40692</v>
+      </c>
+      <c r="G60" t="n">
+        <v>16.92993</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>alte heimat</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3088171/poznan.html</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q268</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ramat Gan</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>gan ramat</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>32.0822</v>
+      </c>
+      <c r="G61" t="n">
+        <v>34.8106</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293788</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q192807</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Heinz_Guttfeld</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ramle</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ramle</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>31.9262</v>
+      </c>
+      <c r="G62" t="n">
+        <v>34.8635</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293768</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q221447</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Recco</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>recco</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Recco</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Italia &gt; Liguria &gt; Polanesi &gt; Recco</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>44.3628</v>
+      </c>
+      <c r="G63" t="n">
+        <v>9.148199999999999</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>transit</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/3169539</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q266648</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>https://de.wikipedia.org/wiki/Schule_am_Mittelmeer</t>
+        </is>
+      </c>
+      <c r="BU63" t="inlineStr">
+        <is>
+          <t>https://vimeo.com/344127667</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
           <t>Rüdnitz</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>rüdnitz</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Brandenburg</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>GO – geographischer Ort &gt; Deutschland &gt; Brandenburg</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
         <v>52.7213</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G64" t="n">
         <v>13.625</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>alte_heimat 
 transit</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>https://www.geonames.org/2843368/ruednitz.html</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q569568</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>https://hachschara.juedische-geschichte-online.net/ueber/hachschara</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>https://www.jewish-places.de/de/DE-MUS-975919Z/facility/2a436a9f-1ad7-4e74-9f48-51946369ecb6/Hachschara---Lager-R%C3%BCdnitz</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Sachsenhausen</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>sachsenhausen</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Oranienburg</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Berlin &gt; Oranienburg</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>52.766</v>
-      </c>
-      <c r="G49" t="n">
-        <v>13.264</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2925534</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q154498</t>
-        </is>
-      </c>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>https://www.sachsenhausen-sbg.de/geschichte/1936-1945-konzentrationslager-sachsenhausen/</t>
-        </is>
-      </c>
-      <c r="BN49" t="inlineStr">
-        <is>
-          <t>https://www.orte-der-erinnerung.de/informationen/das-konzentrationslager-sachsenhausen-1936-1945-ereignisse-und-entwicklungen/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Salzburg</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>salzburg</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Osterreich</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Österreich</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>47.8137</v>
-      </c>
-      <c r="G50" t="n">
-        <v>13.0451</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6930925/salzburg-hauptbahnhof.html</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q694694</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Schlesien</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>schlesien</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>nominatim</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>50.9206028</v>
-      </c>
-      <c r="G51" t="n">
-        <v>16.4946351</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sennfeld (Adelsheim)</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>adelsheim sennfeld</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>49.4014</v>
-      </c>
-      <c r="G52" t="n">
-        <v>9.402200000000001</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2833011/sennfeld.html</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q14531586</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Singapur</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>singapur</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>GO - geographischer Ort</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>geonames</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1.36667</v>
-      </c>
-      <c r="G53" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>transit</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/1880251/republic-of-singapore.html</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q334</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Steinstraße 19,</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>19 steinstraße</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Giessen</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>nominatim</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>50.5894211</v>
-      </c>
-      <c r="G54" t="n">
-        <v>8.671178899999999</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>stuttgart</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Deutschland</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>48.7758</v>
-      </c>
-      <c r="G55" t="n">
-        <v>9.1829</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2825297/stuttgart.html</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1022</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Synagoge am Börneplatz, Frankfurt/M</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>am börneplatz frankfurtm synagoge</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>geonames</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>50.11035</v>
-      </c>
-      <c r="G56" t="n">
-        <v>8.671849999999999</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>alte_heimat</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6553153</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q111620976</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Tel Aviv</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>aviv tel</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Palastina - Israel</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>32.0808</v>
-      </c>
-      <c r="G57" t="n">
-        <v>34.7805</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/293397/tel-aviv.html</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q33935</t>
-        </is>
-      </c>
-      <c r="BD57" t="inlineStr">
-        <is>
-          <t>https://prabook.com/web/paul.alsberg/570050</t>
-        </is>
-      </c>
-      <c r="BE57" t="inlineStr">
-        <is>
-          <t>https://irgun-jeckes.org/english/</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr">
-        <is>
-          <t>https://cris.tau.ac.il/en/organisations/the-chaim-weizmann-institute-for-the-study-of-zionism-and-israel-2/</t>
-        </is>
-      </c>
-      <c r="BG57" t="inlineStr">
-        <is>
-          <t>https://en.jabotinsky.org/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Theresienstadt</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>theresienstadt</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Tschechoslowakei</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Tschechoslowakei</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>50.5136</v>
-      </c>
-      <c r="G58" t="n">
-        <v>14.1497</v>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/12217751/theresienstadt-concentration-camp-and-ghetto.html</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q160175</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Treblinka (Vernichtungslager)</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>treblinka vernichtungslager</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Polen</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Polen</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>52.6303</v>
-      </c>
-      <c r="G59" t="n">
-        <v>22.0492</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/756807/treblinka.html</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q152010</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Triest</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>triest</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Trieste</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Italia &gt; Friuli-Venezia Giulia &gt; Trieste</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>45.6364</v>
-      </c>
-      <c r="G60" t="n">
-        <v>13.774</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>verkehrsmittel</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/9796929/porto-di-trieste.html</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1567848</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>states united</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; USA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>39</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-98</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>neue_heimat</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/6252001/united-states.html</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Walltorstraße 48</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>48 walltorstraße</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Giessen</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>nominatim</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>50.589967</v>
-      </c>
-      <c r="G62" t="n">
-        <v>8.6783959</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>ort_der_zeit</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2920512</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q564579</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Wien</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>wien</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Osterreich</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Österreich</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>48.21</v>
-      </c>
-      <c r="G63" t="n">
-        <v>16.37</v>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q1741</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Wullenweberstraße 11, Berlin-Moabit</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>11 berlinmoabit wullenweberstraße</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Berlin</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>GO – geographischer Ort &gt; Deutschland &gt; Berlin</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>chronotopi</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>52.523</v>
-      </c>
-      <c r="G64" t="n">
-        <v>13.3415</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>https://www.geonames.org/2950159</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q56161165</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>https://www.stolpersteine-berlin.de/de/wullenweberstr/11/auguste-stern</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Wuppertal</t>
+          <t>Sachsenhausen</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>wuppertal</t>
+          <t>sachsenhausen</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Oranienburg</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Berlin &gt; Oranienburg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3946,56 +4057,56 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>51.2562</v>
+        <v>52.766</v>
       </c>
       <c r="G65" t="n">
-        <v>7.1481</v>
+        <v>13.264</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>erinnerungsort</t>
+          <t>ort_der_zeit</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2805753/wuppertal.html</t>
+          <t>https://www.geonames.org/2925534</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q2107</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>https://alte-synagoge-wuppertal.de/fileadmin/user_upload/BAS_Gedenkstaetten_Wuppertal-7.pdf</t>
+          <t>https://www.wikidata.org/wiki/Q154498</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>https://www.sachsenhausen-sbg.de/geschichte/1936-1945-konzentrationslager-sachsenhausen/</t>
+        </is>
+      </c>
+      <c r="BN65" t="inlineStr">
+        <is>
+          <t>https://www.orte-der-erinnerung.de/informationen/das-konzentrationslager-sachsenhausen-1936-1945-ereignisse-und-entwicklungen/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Wölfersheim</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>wölfersheim</t>
+          <t>salzburg</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Osterreich</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Deutschland</t>
+          <t>GO – geographischer Ort &gt; Österreich</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4004,94 +4115,84 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>50.4</v>
+        <v>47.8137</v>
       </c>
       <c r="G66" t="n">
-        <v>8.816700000000001</v>
+        <v>13.0451</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>alte_heimat</t>
+          <t>verkehrsmittel</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/2806852/woelfersheim.html</t>
+          <t>https://www.geonames.org/6930925/salzburg-hauptbahnhof.html</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q634098</t>
+          <t>https://www.wikidata.org/wiki/Q694694</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Yad Vashem</t>
+          <t>Schlesien</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>vashem yad</t>
+          <t>schlesien</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Jerusalem</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>wikidata</t>
+          <t>nominatim</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>31.7744237</v>
+        <v>50.9206028</v>
       </c>
       <c r="G67" t="n">
-        <v>35.1772481</v>
+        <v>16.4946351</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>erinnerungsort</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q156591</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>https://collections.yadvashem.org/en/names/13219727</t>
+          <t>alte_heimat</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Zypern</t>
+          <t>Sennfeld (Adelsheim)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>zypern</t>
+          <t>adelsheim sennfeld</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GO - geographischer Ort</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>GO – geographischer Ort</t>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4100,75 +4201,911 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>35</v>
+        <v>49.4014</v>
       </c>
       <c r="G68" t="n">
-        <v>33</v>
+        <v>9.402200000000001</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>ort_der_zeit</t>
+          <t>alte_heimat</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.geonames.org/146669/republic-of-cyprus.html</t>
+          <t>https://www.geonames.org/2833011/sennfeld.html</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q229</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>https://encyclopedia.ushmm.org/content/en/article/cyprus-detention-camps</t>
+          <t>https://www.wikidata.org/wiki/Q14531586</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>Singapur</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>singapur</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.36667</v>
+      </c>
+      <c r="G69" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>transit</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/1880251/republic-of-singapore.html</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q334</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Steinstraße 19,</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>19 steinstraße</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Giessen</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>50.5894211</v>
+      </c>
+      <c r="G70" t="n">
+        <v>8.671178899999999</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>stuttgart</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>48.7758</v>
+      </c>
+      <c r="G71" t="n">
+        <v>9.1829</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2825297/stuttgart.html</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1022</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Synagoge am Börneplatz, Frankfurt/M</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>am börneplatz frankfurtm synagoge</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Frankfurt am Main</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>geonames</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>50.11035</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8.671849999999999</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6553153</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q111620976</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Tel Aviv</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>aviv tel</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Palastina - Israel</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>32.0808</v>
+      </c>
+      <c r="G73" t="n">
+        <v>34.7805</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/293397/tel-aviv.html</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q33935</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>https://prabook.com/web/paul.alsberg/570050</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr">
+        <is>
+          <t>https://irgun-jeckes.org/english/</t>
+        </is>
+      </c>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>https://cris.tau.ac.il/en/organisations/the-chaim-weizmann-institute-for-the-study-of-zionism-and-israel-2/</t>
+        </is>
+      </c>
+      <c r="BG73" t="inlineStr">
+        <is>
+          <t>https://en.jabotinsky.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Theresienstadt</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>theresienstadt</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tschechoslowakei</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Tschechoslowakei</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>50.5136</v>
+      </c>
+      <c r="G74" t="n">
+        <v>14.1497</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/12217751/theresienstadt-concentration-camp-and-ghetto.html</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q160175</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Treblinka (Vernichtungslager)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>treblinka vernichtungslager</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Polen</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Polen</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>52.6303</v>
+      </c>
+      <c r="G75" t="n">
+        <v>22.0492</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/756807/treblinka.html</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q152010</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Triest</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>triest</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Trieste</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Italia &gt; Friuli-Venezia Giulia &gt; Trieste</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>45.6364</v>
+      </c>
+      <c r="G76" t="n">
+        <v>13.774</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/9796929/porto-di-trieste.html</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1567848</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>states united</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; USA</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>39</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-98</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>neue_heimat</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/6252001/united-states.html</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Walltorstraße 48</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>48 walltorstraße</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Giessen</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Gießen</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>nominatim</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>50.5895607</v>
+      </c>
+      <c r="G78" t="n">
+        <v>8.6775827</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2920512</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q564579</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://www.giessen.de/index.php?ModID=7&amp;FID=2874.2939.1&amp;object=tx%7C2874.2939.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Wien</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>wien</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Osterreich</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Österreich</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="G79" t="n">
+        <v>16.37</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q1741</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Wullenweberstraße 11, Berlin-Moabit</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11 berlinmoabit wullenweberstraße</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland &gt; Berlin</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>52.523</v>
+      </c>
+      <c r="G80" t="n">
+        <v>13.3415</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2950159</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q56161165</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>https://www.stolpersteine-berlin.de/de/wullenweberstr/11/auguste-stern</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Wuppertal</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>wuppertal</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>51.2562</v>
+      </c>
+      <c r="G81" t="n">
+        <v>7.1481</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2805753/wuppertal.html</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q2107</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>https://www.rheinische-geschichte.lvr.de/Persoenlichkeiten/paul-avraham-alsberg-/DE-2086/lido/69aad13fd286f8.35874411#toc-25</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>https://alte-synagoge-wuppertal.de/fileadmin/user_upload/BAS_Gedenkstaetten_Wuppertal-7.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Wölfersheim</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>wölfersheim</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Deutschland</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Deutschland</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.816700000000001</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>alte_heimat</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2806852/woelfersheim.html</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q634098</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Yad Vashem</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>vashem yad</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Jerusalem</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Jerusalem</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>wikidata</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>31.7744237</v>
+      </c>
+      <c r="G83" t="n">
+        <v>35.1772481</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>erinnerungsort</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q156591</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>https://collections.yadvashem.org/en/names/13219727</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Zypern</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>zypern</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GO - geographischer Ort</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>35</v>
+      </c>
+      <c r="G84" t="n">
+        <v>33</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ort_der_zeit</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/146669/republic-of-cyprus.html</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q229</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>https://encyclopedia.ushmm.org/content/en/article/cyprus-detention-camps</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Zürich</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>zürich</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Schweiz</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>GO – geographischer Ort &gt; Schweiz</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>chronotopi</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>47.3666</v>
+      </c>
+      <c r="G85" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>verkehrsmittel</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://www.geonames.org/2657896</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q72</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>Ēmeq Yizrəʿēl</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>yizrəʿēl ēmeq</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Emek (Jesreelebene)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>GO – geographischer Ort &gt; Palästina – Israel &gt; Emek (Jesreelebene)</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>geonames</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F86" t="n">
         <v>32.60417</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G86" t="n">
         <v>35.23639</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>neue_heimat</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>https://www.geonames.org/293165/jezreel-valley.html</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>https://www.wikidata.org/wiki/Q763829</t>
         </is>

--- a/notebook/locations.xlsx
+++ b/notebook/locations.xlsx
@@ -2036,14 +2036,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>geonames</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>50.11</v>
+        <v>50.11035</v>
       </c>
       <c r="G25" t="n">
-        <v>8.68</v>
+        <v>8.671849999999999</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -4691,10 +4691,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>50.5895607</v>
+        <v>50.589967</v>
       </c>
       <c r="G78" t="n">
-        <v>8.6775827</v>
+        <v>8.6783959</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -4740,14 +4740,14 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>chronotopi</t>
+          <t>wikidata</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>48.21</v>
+        <v>48.20833333333334</v>
       </c>
       <c r="G79" t="n">
-        <v>16.37</v>
+        <v>16.3725</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
